--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2246867E-29C4-41FB-B535-B6F2387DB841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09489EC5-AE31-4DD8-B266-780AC9D0DBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
   </bookViews>
@@ -477,7 +477,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09489EC5-AE31-4DD8-B266-780AC9D0DBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4472F5-215D-4FEF-8D59-C2DB5AE694E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
-  <si>
-    <t>NUMERO</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>FECHA</t>
   </si>
@@ -50,9 +47,6 @@
     <t>COTIZACIÓN</t>
   </si>
   <si>
-    <t>SOLICITO</t>
-  </si>
-  <si>
     <t>ID_PROVEEDOR</t>
   </si>
   <si>
@@ -65,20 +59,101 @@
     <t>TIPOCAMBIO</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>EXISTENCIA</t>
+    <t>DOCUMENTO</t>
+  </si>
+  <si>
+    <t>CFDI</t>
+  </si>
+  <si>
+    <t>SOLICITUD</t>
+  </si>
+  <si>
+    <t>PAGO</t>
+  </si>
+  <si>
+    <t>FORMAPAGO</t>
+  </si>
+  <si>
+    <t>METODOPAGO</t>
+  </si>
+  <si>
+    <t>ENTREGAINICIO</t>
+  </si>
+  <si>
+    <t>ENTREGAFINAL</t>
+  </si>
+  <si>
+    <t>DESCUENTO</t>
+  </si>
+  <si>
+    <t>IVA</t>
+  </si>
+  <si>
+    <t>MONEDA</t>
+  </si>
+  <si>
+    <t>NOORDEN</t>
+  </si>
+  <si>
+    <t>FO-SG-04-00</t>
+  </si>
+  <si>
+    <t>AVANTE20260414</t>
+  </si>
+  <si>
+    <t>bimb26</t>
+  </si>
+  <si>
+    <t>G03 - Gastos en general</t>
+  </si>
+  <si>
+    <t>María Luisa Martínez Morales</t>
+  </si>
+  <si>
+    <t>PRUEBA GUARDAR</t>
+  </si>
+  <si>
+    <t>Contado</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>PUE (pago en una sola exhibicion)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>MC. Jesús Alfredo Flores Osorio</t>
+  </si>
+  <si>
+    <t>MXN</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -104,8 +179,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,74 +516,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.54296875" customWidth="1"/>
+    <col min="18" max="18" width="13.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="Q1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>1345</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
+        <v>1356</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46126</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4472F5-215D-4FEF-8D59-C2DB5AE694E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9FBEDF-3580-4B14-89DD-C9930292549F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
   <si>
     <t>FECHA</t>
   </si>
@@ -138,6 +138,36 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>BIMB26</t>
+  </si>
+  <si>
+    <t>FINAL</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>18.56</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SUBTOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -516,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
@@ -538,7 +568,7 @@
     <col min="18" max="18" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -596,8 +626,17 @@
       <c r="S1" t="s">
         <v>6</v>
       </c>
+      <c r="T1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U1" t="s">
+        <v>16</v>
+      </c>
+      <c r="V1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1356</v>
       </c>
@@ -654,6 +693,70 @@
       </c>
       <c r="S2" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1357</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U4" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9FBEDF-3580-4B14-89DD-C9930292549F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83ACD560-F4E9-48A5-82A2-88707FE9B623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="45">
   <si>
     <t>FECHA</t>
   </si>
@@ -140,40 +140,46 @@
     <t/>
   </si>
   <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SUBTOTAL</t>
+  </si>
+  <si>
+    <t>AVANTE20260415</t>
+  </si>
+  <si>
     <t>BIMB26</t>
   </si>
   <si>
-    <t>FINAL</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>18.56</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>SUBTOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>PRUEBA BASE</t>
+  </si>
+  <si>
+    <t>$ 8,184.15</t>
+  </si>
+  <si>
+    <t>$ 1,309.46</t>
+  </si>
+  <si>
+    <t>$ 9,493.61</t>
+  </si>
+  <si>
+    <t>$ 4,275.02</t>
+  </si>
+  <si>
+    <t>$ 684.00</t>
+  </si>
+  <si>
+    <t>$ 4,959.02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/MM/yyyy"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -209,9 +215,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,26 +555,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.54296875" customWidth="1"/>
-    <col min="18" max="18" width="13.7265625" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="9.54296875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.0" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.0" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.1796875" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.7265625" collapsed="true"/>
+    <col min="6" max="7" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.90625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.6328125" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="13.0" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="13.7265625" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="13.1796875" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="20.1796875" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="12.0" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
+    <col min="17" max="17" customWidth="true" width="13.54296875" collapsed="true"/>
+    <col min="18" max="18" customWidth="true" width="13.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.35">
@@ -627,13 +636,13 @@
         <v>6</v>
       </c>
       <c r="T1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="U1" t="s">
         <v>16</v>
       </c>
       <c r="V1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
@@ -700,16 +709,16 @@
         <v>1357</v>
       </c>
       <c r="B3" s="1">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
@@ -718,7 +727,7 @@
         <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I3" t="s">
         <v>25</v>
@@ -730,13 +739,13 @@
         <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="N3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O3" t="s">
         <v>30</v>
@@ -748,15 +757,223 @@
         <v>31</v>
       </c>
       <c r="R3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" t="s">
         <v>39</v>
       </c>
-      <c r="S3" t="s">
+      <c r="U3" t="s">
         <v>40</v>
       </c>
+      <c r="V3" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1358.0</v>
+      </c>
+      <c r="B4" t="n" s="2">
+        <v>46127.0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" t="s">
+        <v>39</v>
+      </c>
       <c r="U4" t="s">
+        <v>40</v>
+      </c>
+      <c r="V4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1359.0</v>
+      </c>
+      <c r="B5" t="n" s="3">
+        <v>46127.0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5" t="s">
+        <v>39</v>
+      </c>
+      <c r="U5" t="s">
+        <v>40</v>
+      </c>
+      <c r="V5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1360.0</v>
+      </c>
+      <c r="B6" t="n" s="4">
+        <v>46127.0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" t="s">
+        <v>33</v>
+      </c>
+      <c r="T6" t="s">
+        <v>42</v>
+      </c>
+      <c r="U6" t="s">
         <v>43</v>
+      </c>
+      <c r="V6" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="55">
   <si>
     <t>FECHA</t>
   </si>
@@ -171,6 +171,36 @@
   </si>
   <si>
     <t>$ 4,959.02</t>
+  </si>
+  <si>
+    <t>G02 - Devoluciones, descuentos o bonificaciones</t>
+  </si>
+  <si>
+    <t>FINAL</t>
+  </si>
+  <si>
+    <t>Crédito</t>
+  </si>
+  <si>
+    <t>PPD (pago por partes)</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Adderly</t>
+  </si>
+  <si>
+    <t>$ 3,909.13</t>
+  </si>
+  <si>
+    <t>$ 625.46</t>
+  </si>
+  <si>
+    <t>$ 4,534.59</t>
   </si>
 </sst>
 </file>
@@ -215,9 +245,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -555,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="9.54296875" collapsed="true"/>
@@ -976,6 +1007,74 @@
         <v>44</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1361.0</v>
+      </c>
+      <c r="B7" t="n" s="5">
+        <v>46127.0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>51</v>
+      </c>
+      <c r="R7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U7" t="s">
+        <v>53</v>
+      </c>
+      <c r="V7" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83ACD560-F4E9-48A5-82A2-88707FE9B623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AD64EC-0395-47B7-B9D1-BAEF62365138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
   <si>
     <t>FECHA</t>
   </si>
@@ -95,13 +95,19 @@
     <t>NOORDEN</t>
   </si>
   <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SUBTOTAL</t>
+  </si>
+  <si>
     <t>FO-SG-04-00</t>
   </si>
   <si>
-    <t>AVANTE20260414</t>
-  </si>
-  <si>
-    <t>bimb26</t>
+    <t>AVANTE20260415</t>
+  </si>
+  <si>
+    <t>BIMB26</t>
   </si>
   <si>
     <t>G03 - Gastos en general</t>
@@ -110,19 +116,22 @@
     <t>María Luisa Martínez Morales</t>
   </si>
   <si>
-    <t>PRUEBA GUARDAR</t>
+    <t>PRUEBA</t>
   </si>
   <si>
     <t>Contado</t>
   </si>
   <si>
-    <t>Efectivo</t>
+    <t>Transferencia Electrónica</t>
   </si>
   <si>
     <t>PUE (pago en una sola exhibicion)</t>
   </si>
   <si>
-    <t>1</t>
+    <t>22</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>0</t>
@@ -131,30 +140,33 @@
     <t>SI</t>
   </si>
   <si>
+    <t>Adderly</t>
+  </si>
+  <si>
+    <t>MXN</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>$ 3,909.13</t>
+  </si>
+  <si>
+    <t>$ 625.46</t>
+  </si>
+  <si>
+    <t>$ 4,534.59</t>
+  </si>
+  <si>
+    <t>PROYECTA</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>MC. Jesús Alfredo Flores Osorio</t>
   </si>
   <si>
-    <t>MXN</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>SUBTOTAL</t>
-  </si>
-  <si>
-    <t>AVANTE20260415</t>
-  </si>
-  <si>
-    <t>BIMB26</t>
-  </si>
-  <si>
-    <t>PRUEBA BASE</t>
-  </si>
-  <si>
     <t>$ 8,184.15</t>
   </si>
   <si>
@@ -164,43 +176,16 @@
     <t>$ 9,493.61</t>
   </si>
   <si>
-    <t>$ 4,275.02</t>
-  </si>
-  <si>
-    <t>$ 684.00</t>
-  </si>
-  <si>
-    <t>$ 4,959.02</t>
-  </si>
-  <si>
-    <t>G02 - Devoluciones, descuentos o bonificaciones</t>
-  </si>
-  <si>
-    <t>FINAL</t>
-  </si>
-  <si>
-    <t>Crédito</t>
-  </si>
-  <si>
-    <t>PPD (pago por partes)</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Adderly</t>
-  </si>
-  <si>
-    <t>$ 3,909.13</t>
-  </si>
-  <si>
-    <t>$ 625.46</t>
-  </si>
-  <si>
-    <t>$ 4,534.59</t>
+    <t>PRUEBA FINAL</t>
+  </si>
+  <si>
+    <t>Por definir</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Luis Angel Lira</t>
   </si>
 </sst>
 </file>
@@ -245,11 +230,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
@@ -586,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="9.54296875" collapsed="true"/>
@@ -667,412 +650,217 @@
         <v>6</v>
       </c>
       <c r="T1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="U1" t="s">
         <v>16</v>
       </c>
       <c r="V1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>1356</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="n" s="2">
+        <v>46127.0</v>
+      </c>
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F3" t="s">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G3" t="s">
         <v>25</v>
       </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="H3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
         <v>27</v>
       </c>
-      <c r="L2" t="s">
+      <c r="J3" t="s">
         <v>28</v>
       </c>
-      <c r="M2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="K3" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s">
         <v>31</v>
       </c>
-      <c r="R2" t="s">
+      <c r="N3" t="s">
         <v>32</v>
       </c>
-      <c r="S2" t="s">
+      <c r="O3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>1357</v>
-      </c>
-      <c r="B3" s="1">
-        <v>46127</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="P3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" t="s">
         <v>36</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3" t="s">
-        <v>32</v>
-      </c>
-      <c r="S3" t="s">
-        <v>33</v>
-      </c>
       <c r="T3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="U3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="V3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1358.0</v>
-      </c>
-      <c r="B4" t="n" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="n" s="3">
         <v>46127.0</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" t="s">
         <v>36</v>
       </c>
-      <c r="E4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R4" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" t="s">
-        <v>33</v>
-      </c>
       <c r="T4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="U4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="V4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1359.0</v>
-      </c>
-      <c r="B5" t="n" s="3">
-        <v>46127.0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>31</v>
-      </c>
-      <c r="R5" t="s">
-        <v>32</v>
-      </c>
-      <c r="S5" t="s">
-        <v>33</v>
-      </c>
-      <c r="T5" t="s">
-        <v>39</v>
-      </c>
-      <c r="U5" t="s">
-        <v>40</v>
-      </c>
-      <c r="V5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1360.0</v>
-      </c>
-      <c r="B6" t="n" s="4">
-        <v>46127.0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S6" t="s">
-        <v>33</v>
-      </c>
-      <c r="T6" t="s">
-        <v>42</v>
-      </c>
-      <c r="U6" t="s">
-        <v>43</v>
-      </c>
-      <c r="V6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1361.0</v>
-      </c>
-      <c r="B7" t="n" s="5">
-        <v>46127.0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
         <v>45</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L7" t="s">
-        <v>49</v>
-      </c>
-      <c r="M7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R7" t="s">
-        <v>32</v>
-      </c>
-      <c r="S7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T7" t="s">
-        <v>52</v>
-      </c>
-      <c r="U7" t="s">
-        <v>53</v>
-      </c>
-      <c r="V7" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="70">
   <si>
     <t>FECHA</t>
   </si>
@@ -186,6 +186,66 @@
   </si>
   <si>
     <t>Luis Angel Lira</t>
+  </si>
+  <si>
+    <t>AVANTE20260416</t>
+  </si>
+  <si>
+    <t>LACT01</t>
+  </si>
+  <si>
+    <t>PRUEBA DOS</t>
+  </si>
+  <si>
+    <t>Crédito</t>
+  </si>
+  <si>
+    <t>Tarjeta de Crédito</t>
+  </si>
+  <si>
+    <t>PPD (pago por partes)</t>
+  </si>
+  <si>
+    <t>$ 6,046.64</t>
+  </si>
+  <si>
+    <t>$ 967.46</t>
+  </si>
+  <si>
+    <t>$ 7,014.10</t>
+  </si>
+  <si>
+    <t>jume06</t>
+  </si>
+  <si>
+    <t>GRANDE</t>
+  </si>
+  <si>
+    <t>$ 20,795.79</t>
+  </si>
+  <si>
+    <t>$ 3,327.33</t>
+  </si>
+  <si>
+    <t>$ 24,123.12</t>
+  </si>
+  <si>
+    <t>bacha07</t>
+  </si>
+  <si>
+    <t>PRUEBA FINAL 123</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>$ 5,240.62</t>
+  </si>
+  <si>
+    <t>$ 838.50</t>
+  </si>
+  <si>
+    <t>$ 6,079.12</t>
   </si>
 </sst>
 </file>
@@ -230,9 +290,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
@@ -569,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="9.54296875" collapsed="true"/>
@@ -863,6 +926,210 @@
         <v>45</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="n" s="4">
+        <v>46128.0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>42</v>
+      </c>
+      <c r="R5" t="s">
+        <v>35</v>
+      </c>
+      <c r="S5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" t="s">
+        <v>56</v>
+      </c>
+      <c r="U5" t="s">
+        <v>57</v>
+      </c>
+      <c r="V5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="n" s="5">
+        <v>46128.0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>42</v>
+      </c>
+      <c r="R6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" t="s">
+        <v>61</v>
+      </c>
+      <c r="U6" t="s">
+        <v>62</v>
+      </c>
+      <c r="V6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="n" s="6">
+        <v>46128.54262923611</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s">
+        <v>66</v>
+      </c>
+      <c r="N7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R7" t="s">
+        <v>35</v>
+      </c>
+      <c r="S7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" t="s">
+        <v>67</v>
+      </c>
+      <c r="U7" t="s">
+        <v>68</v>
+      </c>
+      <c r="V7" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="81">
   <si>
     <t>FECHA</t>
   </si>
@@ -246,6 +246,39 @@
   </si>
   <si>
     <t>$ 6,079.12</t>
+  </si>
+  <si>
+    <t>avsu15</t>
+  </si>
+  <si>
+    <t>FINABIEN-001-2025</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>FO-SG-04-0888</t>
+  </si>
+  <si>
+    <t>AVANTE20260417</t>
+  </si>
+  <si>
+    <t>bimb26</t>
+  </si>
+  <si>
+    <t>NOMBRE DOCUMENTO</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>$ 486.25</t>
+  </si>
+  <si>
+    <t>$ 77.80</t>
+  </si>
+  <si>
+    <t>$ 564.05</t>
   </si>
 </sst>
 </file>
@@ -290,9 +323,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -632,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="9.54296875" collapsed="true"/>
@@ -1130,6 +1165,142 @@
         <v>69</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="n" s="7">
+        <v>46128.551586458336</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>42</v>
+      </c>
+      <c r="R8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" t="s">
+        <v>43</v>
+      </c>
+      <c r="U8" t="s">
+        <v>44</v>
+      </c>
+      <c r="V8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="n" s="8">
+        <v>46129.47698445602</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9" t="s">
+        <v>77</v>
+      </c>
+      <c r="N9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>42</v>
+      </c>
+      <c r="R9" t="s">
+        <v>35</v>
+      </c>
+      <c r="S9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" t="s">
+        <v>78</v>
+      </c>
+      <c r="U9" t="s">
+        <v>79</v>
+      </c>
+      <c r="V9" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="82">
   <si>
     <t>FECHA</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>$ 564.05</t>
+  </si>
+  <si>
+    <t>CAMBIOS</t>
   </si>
 </sst>
 </file>
@@ -323,9 +326,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -1033,7 +1037,7 @@
       <c r="A6" t="n">
         <v>5.0</v>
       </c>
-      <c r="B6" t="n" s="5">
+      <c r="B6" t="n" s="9">
         <v>46128.0</v>
       </c>
       <c r="C6" t="s">
@@ -1052,7 +1056,7 @@
         <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="I6" t="s">
         <v>53</v>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="93">
   <si>
     <t>FECHA</t>
   </si>
@@ -282,6 +282,39 @@
   </si>
   <si>
     <t>CAMBIOS</t>
+  </si>
+  <si>
+    <t>CAMBIOS ACTUALES</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>17.65</t>
+  </si>
+  <si>
+    <t>USD $ 342.59</t>
+  </si>
+  <si>
+    <t>USD $ 54.81</t>
+  </si>
+  <si>
+    <t>USD $ 397.40</t>
+  </si>
+  <si>
+    <t>PROYECTA123</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>$ 3,930.32</t>
+  </si>
+  <si>
+    <t>$ 628.85</t>
+  </si>
+  <si>
+    <t>$ 4,559.17</t>
   </si>
 </sst>
 </file>
@@ -326,9 +359,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -833,7 +869,7 @@
       <c r="A3" t="n">
         <v>2.0</v>
       </c>
-      <c r="B3" t="n" s="2">
+      <c r="B3" t="n" s="12">
         <v>46127.0</v>
       </c>
       <c r="C3" t="s">
@@ -852,7 +888,7 @@
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="I3" t="s">
         <v>27</v>
@@ -870,7 +906,7 @@
         <v>31</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="O3" t="s">
         <v>33</v>
@@ -888,13 +924,13 @@
         <v>36</v>
       </c>
       <c r="T3" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="U3" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="V3" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
@@ -969,7 +1005,7 @@
       <c r="A5" t="n">
         <v>4.0</v>
       </c>
-      <c r="B5" t="n" s="4">
+      <c r="B5" t="n" s="11">
         <v>46128.0</v>
       </c>
       <c r="C5" t="s">
@@ -988,7 +1024,7 @@
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="I5" t="s">
         <v>53</v>
@@ -1006,7 +1042,7 @@
         <v>31</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O5" t="s">
         <v>33</v>
@@ -1018,19 +1054,19 @@
         <v>42</v>
       </c>
       <c r="R5" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="S5" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="T5" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="U5" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="V5" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
